--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -8316,16 +8316,16 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O49" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.974478179659193</v>
+        <v>1.992266271367834</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O50" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -9304,16 +9304,16 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>822</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>171</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>3.041763682177675</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -2049,9 +2043,6 @@
       <c r="O10" t="n">
         <v>91</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>1.618716345486365</v>
       </c>
@@ -2445,9 +2436,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3333,9 +3321,6 @@
       <c r="O18" t="n">
         <v>35</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.6225832098024481</v>
       </c>
@@ -3729,9 +3714,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4469,9 +4451,6 @@
       <c r="O25" t="n">
         <v>71</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.0332455111015389</v>
       </c>
@@ -4617,9 +4596,6 @@
       <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.9427688605579929</v>
       </c>
@@ -5013,9 +4989,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5753,9 +5726,6 @@
       <c r="O33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.002341233176164712</v>
       </c>
@@ -5901,9 +5871,6 @@
       <c r="O34" t="n">
         <v>81</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.440835428399951</v>
       </c>
@@ -6297,9 +6264,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7185,9 +7149,6 @@
       <c r="O42" t="n">
         <v>93</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.654292528903648</v>
       </c>
@@ -7581,9 +7542,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7729,9 +7687,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7877,9 +7832,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8025,9 +7977,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8173,9 +8122,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8321,9 +8267,6 @@
       <c r="O49" t="n">
         <v>112</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>1.992266271367834</v>
       </c>
@@ -8717,9 +8660,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8865,9 +8805,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9013,9 +8950,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9161,9 +9095,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9304,16 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4091261092987516</v>
+        <v>0.4802784761333171</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9466,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O56" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9811,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O55" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4802784761333171</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O56" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>840</v>
+        <v>849</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="O55" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R55" t="n">
-        <v>0.6403713015110895</v>
+        <v>0.7648879434715791</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="O56" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O55" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="R55" t="n">
-        <v>0.7648879434715791</v>
+        <v>0.8360403103061447</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O56" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O55" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R55" t="n">
-        <v>0.8360403103061447</v>
+        <v>0.8538284020147859</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O55" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="R55" t="n">
-        <v>0.8538284020147859</v>
+        <v>0.9605569522666343</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O56" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="O55" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="R55" t="n">
-        <v>0.9605569522666343</v>
+        <v>1.138437869353048</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="O56" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>867</v>
+        <v>877</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="O55" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="R55" t="n">
-        <v>1.138437869353048</v>
+        <v>1.245166419604896</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="O56" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="O55" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="R55" t="n">
-        <v>1.245166419604896</v>
+        <v>1.529775886943158</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="O56" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>883</v>
+        <v>899</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O55" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="R55" t="n">
-        <v>1.529775886943158</v>
+        <v>1.636504437195006</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O56" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>899</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -8616,12 +8616,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8694,42 +8694,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9226,104 +9226,90 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.636504437195006</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9336,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9399,98 +9385,23 @@
       <c r="O56" t="n">
         <v>92</v>
       </c>
+      <c r="R56" t="n">
+        <v>1.636504437195006</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1600</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Puumala-virus</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN56" t="b">
-        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -9556,6 +9467,240 @@
         </is>
       </c>
       <c r="BC56" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>92</v>
+      </c>
+      <c r="O57" t="n">
+        <v>92</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Puumala-virus</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -9677,7 +9822,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -9687,7 +9832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -798,17 +798,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1032,17 +1037,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -2068,7 +2078,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2076,17 +2086,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2302,7 +2317,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2310,17 +2325,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3346,7 +3366,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3354,17 +3374,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3580,7 +3605,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -3588,17 +3613,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4621,7 +4651,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -4629,17 +4659,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4855,7 +4890,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -4863,17 +4898,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5896,7 +5936,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -5904,17 +5944,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6130,7 +6175,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6138,17 +6183,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7174,7 +7224,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7182,17 +7232,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7408,7 +7463,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -7416,17 +7471,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8292,7 +8352,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -8300,17 +8360,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8526,7 +8591,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -8534,17 +8599,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9410,7 +9480,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -9418,17 +9488,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9644,7 +9719,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -9652,17 +9727,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1600</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">

--- a/diseases/d102/2026-2029.xlsx
+++ b/diseases/d102/2026-2029.xlsx
@@ -9450,13 +9450,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="O56" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="R56" t="n">
-        <v>1.636504437195006</v>
+        <v>1.921113904533269</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="O57" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9781,6 +9781,409 @@
         </is>
       </c>
       <c r="BC57" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hantavirus-infection</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Puumala-virus</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Etiology-specific subset of hantavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1600</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -9819,7 +10222,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -9902,7 +10305,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -9912,7 +10315,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -9932,7 +10335,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -9964,7 +10367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>905</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16">
